--- a/artfynd/A 61742-2023 artfynd.xlsx
+++ b/artfynd/A 61742-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129221381</v>
+        <v>129221383</v>
       </c>
       <c r="B2" t="n">
-        <v>8439</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>2079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>317192</v>
+        <v>317194</v>
       </c>
       <c r="R2" t="n">
-        <v>6550560</v>
+        <v>6550535</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -764,17 +759,17 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -789,6 +784,560 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124322083</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>317141</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6550562</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Larsson, Urban Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129221382</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>317206</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6550532</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129221380</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>317217</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6550559</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129221384</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>317194</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6550535</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129221381</v>
+      </c>
+      <c r="B7" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norra Rävmarken, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>317192</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6550560</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61742-2023 artfynd.xlsx
+++ b/artfynd/A 61742-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221383</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124322083</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221380</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221384</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,8 +1368,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129221381</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>